--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9450,13 +9450,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="O56" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="R56" t="n">
-        <v>1.921113904533269</v>
+        <v>2.063418638202399</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="O57" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R58" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O59" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>940</v>
+        <v>944</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9450,13 +9450,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O56" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R56" t="n">
-        <v>2.063418638202399</v>
+        <v>2.081206729911041</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O57" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R58" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O59" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O58" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="R58" t="n">
-        <v>0.426914201007393</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>954</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9853,13 +9853,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O58" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R58" t="n">
-        <v>0.569218934676524</v>
+        <v>0.6225832098024481</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O59" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -10189,6 +10189,151 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10222,7 +10367,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10450,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -10315,7 +10460,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -10367,7 +10512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9814,12 +9814,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9844,109 +9844,90 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.6225832098024481</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9954,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10017,103 +9998,28 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="O59" t="n">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.227378327896255</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Puumala-virus</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -10212,123 +10118,362 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>69</v>
+      </c>
+      <c r="O60" t="n">
+        <v>69</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Puumala-virus</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>D102</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Hantavirus infection</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>汉坦病毒感染</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N60" t="n">
+      <c r="N61" t="n">
         <v>1</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="R60" t="n">
+      <c r="R61" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP60" t="inlineStr">
+      <c r="AP61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr"/>
-      <c r="AT60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV60" t="inlineStr">
+      <c r="AV61" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW60" t="inlineStr">
+      <c r="AW61" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr">
+      <c r="AY61" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA60" t="inlineStr">
+      <c r="BA61" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB60" t="inlineStr">
+      <c r="BB61" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC60" t="inlineStr">
+      <c r="BC61" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -10450,7 +10595,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -10460,7 +10605,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -10512,7 +10657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>966</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="O59" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="R59" t="n">
-        <v>1.227378327896255</v>
+        <v>1.600928253777724</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="O60" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -10476,6 +10476,409 @@
       <c r="BC61" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Puumala-virus</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10998,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -10605,7 +11008,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -10625,7 +11028,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -10657,7 +11060,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1000</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -10546,13 +10546,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4848,6 +4983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4996,6 +5136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5144,6 +5289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5292,6 +5442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5440,6 +5595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5588,6 +5748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5733,6 +5898,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5869,6 +6039,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6005,6 +6180,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6141,6 +6321,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6277,6 +6462,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6413,6 +6603,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6549,6 +6744,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6685,6 +6885,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6821,6 +7026,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6957,6 +7167,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7093,6 +7308,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7229,6 +7449,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7365,6 +7590,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7501,6 +7731,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7637,6 +7872,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7773,6 +8013,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7909,6 +8154,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8045,6 +8295,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8181,6 +8436,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8317,6 +8577,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8453,6 +8718,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8589,6 +8859,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8725,6 +9000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8861,6 +9141,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8997,6 +9282,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9133,6 +9423,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9269,6 +9564,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9808,6 +10108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9956,6 +10261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10104,6 +10414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10252,6 +10567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10400,6 +10720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10548,6 +10873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10693,6 +11023,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10829,6 +11164,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10965,6 +11305,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11101,6 +11446,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11237,6 +11587,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11373,6 +11728,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11509,6 +11869,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11645,6 +12010,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11781,6 +12151,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11917,6 +12292,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12053,6 +12433,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12189,6 +12574,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12325,6 +12715,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12461,6 +12856,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12597,6 +12997,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12733,6 +13138,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12869,6 +13279,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13005,6 +13420,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13141,6 +13561,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13277,6 +13702,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13413,6 +13843,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13549,6 +13984,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13685,6 +14125,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13821,6 +14266,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13957,6 +14407,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14093,6 +14548,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14229,6 +14689,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14768,6 +15233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14916,6 +15386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15064,6 +15539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15212,6 +15692,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15360,6 +15845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15505,6 +15995,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15650,6 +16145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15786,6 +16286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15922,6 +16427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16058,6 +16568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16194,6 +16709,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16330,6 +16850,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16466,6 +16991,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16602,6 +17132,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16738,6 +17273,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16874,6 +17414,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17010,6 +17555,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17146,6 +17696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17282,6 +17837,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17418,6 +17978,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17554,6 +18119,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17690,6 +18260,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17826,6 +18401,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17962,6 +18542,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18098,6 +18683,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18234,6 +18824,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18370,6 +18965,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18506,6 +19106,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18642,6 +19247,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18778,6 +19388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18914,6 +19529,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19050,6 +19670,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19186,6 +19811,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19725,6 +20355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19873,6 +20508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20021,6 +20661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20169,6 +20814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20317,6 +20967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20462,6 +21117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20607,6 +21267,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20743,6 +21408,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20879,6 +21549,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21015,6 +21690,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21151,6 +21831,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21287,6 +21972,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21423,6 +22113,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21559,6 +22254,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21695,6 +22395,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21831,6 +22536,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21967,6 +22677,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22103,6 +22818,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22239,6 +22959,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22375,6 +23100,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22511,6 +23241,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22647,6 +23382,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22783,6 +23523,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22919,6 +23664,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23055,6 +23805,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23191,6 +23946,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23327,6 +24087,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23463,6 +24228,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23599,6 +24369,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23735,6 +24510,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23871,6 +24651,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24007,6 +24792,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24143,6 +24933,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24682,6 +25477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24830,6 +25630,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24978,6 +25783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25126,6 +25936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25274,6 +26089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25422,6 +26242,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25970,6 +26795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26115,6 +26945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26260,6 +27095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26405,6 +27245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26550,6 +27395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27098,6 +27948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27243,6 +28098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27388,6 +28248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27533,6 +28398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27678,6 +28548,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28226,6 +29101,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28358,13 +29238,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O194" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R194" t="n">
-        <v>1.600928253777724</v>
+        <v>1.689868712320931</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -28522,10 +29402,10 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O195" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
@@ -28774,6 +29654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28906,13 +29791,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O197" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R197" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -29070,10 +29955,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O198" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -29420,7 +30305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1347</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -29791,13 +29791,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O197" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R197" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -29955,10 +29955,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O198" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1361</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -29791,13 +29791,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O197" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R197" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -29955,10 +29955,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O198" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1365</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -15528,9 +15528,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0002865038132769385</v>
       </c>

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -43057,13 +43057,13 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R314" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
@@ -44332,13 +44332,13 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O323" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R323" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.7115236683456551</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1719</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -4446,17 +4446,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4469,22 +4467,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4881,17 +4869,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4904,22 +4890,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5175,17 +5151,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5198,22 +5172,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5610,17 +5574,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5633,22 +5595,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6045,17 +5997,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6068,22 +6018,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -10161,17 +10101,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10184,22 +10122,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10737,17 +10665,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10760,22 +10686,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11172,17 +11088,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11195,22 +11109,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11607,17 +11511,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11630,22 +11532,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -15720,17 +15612,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15743,22 +15633,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16014,14 +15894,12 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
       <c r="R118" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16034,22 +15912,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -16446,17 +16314,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16469,22 +16335,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -16881,17 +16737,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16904,22 +16758,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -21132,17 +20976,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21155,22 +20997,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -21285,17 +21117,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21308,22 +21138,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -21861,17 +21681,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21884,22 +21702,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -22437,17 +22245,15 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22460,22 +22266,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -26829,17 +26625,15 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26852,22 +26646,12 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -27546,17 +27330,15 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27569,22 +27351,12 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -28263,17 +28035,15 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28286,22 +28056,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -28980,17 +28740,15 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
       <c r="Q215" t="n">
         <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29003,22 +28761,12 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -29415,17 +29163,15 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29438,22 +29184,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -30411,14 +30147,12 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30431,22 +30165,12 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -31407,14 +31131,12 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31427,22 +31149,12 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -32121,14 +31833,12 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32141,22 +31851,12 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
-      </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -32835,14 +32535,12 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32855,22 +32553,12 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
@@ -33828,14 +33516,12 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33848,22 +33534,12 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
-      </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -34542,14 +34218,12 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34562,22 +34236,12 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
-      </c>
-      <c r="AU254" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -35256,14 +34920,12 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35276,22 +34938,12 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
-      </c>
-      <c r="AU259" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -36111,14 +35763,12 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36131,22 +35781,12 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
-      </c>
-      <c r="AU265" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -42345,14 +41985,12 @@
       <c r="O309" t="n">
         <v>1</v>
       </c>
+      <c r="P309" t="n">
+        <v>1</v>
+      </c>
       <c r="R309" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA309" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -42365,22 +42003,12 @@
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR309" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="n">
         <v>0</v>
-      </c>
-      <c r="AU309" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -43960,13 +43960,13 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O323" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="R323" t="n">
-        <v>0.7115236683456551</v>
+        <v>0.8182522185975032</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1726</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -42685,13 +42685,13 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O314" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R314" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -43960,13 +43960,13 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O323" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="R323" t="n">
-        <v>0.8182522185975032</v>
+        <v>0.9783450439752756</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -45168,6 +45168,150 @@
       <c r="BC331" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>2</v>
+      </c>
+      <c r="O332" t="n">
+        <v>2</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0.002391078655990946</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr">
+        <is>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+        </is>
+      </c>
+      <c r="AT332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA332" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -45204,7 +45348,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -45287,7 +45431,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -45297,7 +45441,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11">
@@ -45349,7 +45493,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1733</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="16">
